--- a/r5-core-21-krankenanstaltennummer-identifier-is-missing-from-r5-hl7-at-core-organization-profile/StructureDefinition-at-core-valueset.xlsx
+++ b/r5-core-21-krankenanstaltennummer-identifier-is-missing-from-r5-hl7-at-core-organization-profile/StructureDefinition-at-core-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T14:43:49+00:00</t>
+    <t>2024-10-30T14:17:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
